--- a/Dataset/CRASH2_Final_Dataset.xlsx
+++ b/Dataset/CRASH2_Final_Dataset.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9df439e20db99215/Desktop/ML_Project/DetaSet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9F59CC08-462E-4877-851B-B59F088943C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="8_{9F59CC08-462E-4877-851B-B59F088943C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EBC1CC8-5AB7-475C-969B-D0DDD4EF2414}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$1001</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -3415,6 +3418,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N1001"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -3611,9 +3630,6 @@
       <c r="F5">
         <v>10</v>
       </c>
-      <c r="G5">
-        <v>13</v>
-      </c>
       <c r="H5" t="s">
         <v>16</v>
       </c>
@@ -3655,9 +3671,6 @@
       <c r="F6">
         <v>18</v>
       </c>
-      <c r="G6">
-        <v>13</v>
-      </c>
       <c r="H6" t="s">
         <v>16</v>
       </c>
@@ -3963,9 +3976,6 @@
       <c r="F13">
         <v>22</v>
       </c>
-      <c r="G13">
-        <v>9</v>
-      </c>
       <c r="H13" t="s">
         <v>16</v>
       </c>
@@ -4007,9 +4017,6 @@
       <c r="F14">
         <v>18</v>
       </c>
-      <c r="G14">
-        <v>7</v>
-      </c>
       <c r="H14" t="s">
         <v>16</v>
       </c>
@@ -4227,9 +4234,6 @@
       <c r="F19">
         <v>18</v>
       </c>
-      <c r="G19">
-        <v>9</v>
-      </c>
       <c r="H19" t="s">
         <v>16</v>
       </c>
@@ -4271,9 +4275,6 @@
       <c r="F20">
         <v>16</v>
       </c>
-      <c r="G20">
-        <v>8</v>
-      </c>
       <c r="H20" t="s">
         <v>16</v>
       </c>
@@ -4359,9 +4360,6 @@
       <c r="F22">
         <v>17</v>
       </c>
-      <c r="G22">
-        <v>7</v>
-      </c>
       <c r="H22" t="s">
         <v>23</v>
       </c>
@@ -4667,9 +4665,6 @@
       <c r="F29">
         <v>26</v>
       </c>
-      <c r="G29">
-        <v>11</v>
-      </c>
       <c r="H29" t="s">
         <v>23</v>
       </c>
@@ -4799,9 +4794,6 @@
       <c r="F32">
         <v>18</v>
       </c>
-      <c r="G32">
-        <v>9</v>
-      </c>
       <c r="H32" t="s">
         <v>16</v>
       </c>
@@ -4975,9 +4967,6 @@
       <c r="F36">
         <v>15</v>
       </c>
-      <c r="G36">
-        <v>13</v>
-      </c>
       <c r="H36" t="s">
         <v>23</v>
       </c>
@@ -5063,9 +5052,6 @@
       <c r="F38">
         <v>15</v>
       </c>
-      <c r="G38">
-        <v>13</v>
-      </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
@@ -5151,9 +5137,6 @@
       <c r="F40">
         <v>14</v>
       </c>
-      <c r="G40">
-        <v>13</v>
-      </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
@@ -5195,9 +5178,6 @@
       <c r="F41">
         <v>18</v>
       </c>
-      <c r="G41">
-        <v>8</v>
-      </c>
       <c r="H41" t="s">
         <v>23</v>
       </c>
@@ -5283,9 +5263,6 @@
       <c r="F43">
         <v>19</v>
       </c>
-      <c r="G43">
-        <v>13</v>
-      </c>
       <c r="H43" t="s">
         <v>23</v>
       </c>
@@ -5371,9 +5348,6 @@
       <c r="F45">
         <v>20</v>
       </c>
-      <c r="G45">
-        <v>13</v>
-      </c>
       <c r="H45" t="s">
         <v>16</v>
       </c>
@@ -5459,9 +5433,6 @@
       <c r="F47">
         <v>15</v>
       </c>
-      <c r="G47">
-        <v>13</v>
-      </c>
       <c r="H47" t="s">
         <v>23</v>
       </c>
@@ -5635,9 +5606,6 @@
       <c r="F51">
         <v>10</v>
       </c>
-      <c r="G51">
-        <v>13</v>
-      </c>
       <c r="H51" t="s">
         <v>16</v>
       </c>
@@ -5767,9 +5735,6 @@
       <c r="F54">
         <v>17</v>
       </c>
-      <c r="G54">
-        <v>8</v>
-      </c>
       <c r="H54" t="s">
         <v>23</v>
       </c>
@@ -5855,9 +5820,6 @@
       <c r="F56">
         <v>32</v>
       </c>
-      <c r="G56">
-        <v>5</v>
-      </c>
       <c r="H56" t="s">
         <v>23</v>
       </c>
@@ -5943,9 +5905,6 @@
       <c r="F58">
         <v>13</v>
       </c>
-      <c r="G58">
-        <v>13</v>
-      </c>
       <c r="H58" t="s">
         <v>16</v>
       </c>
@@ -6031,9 +5990,6 @@
       <c r="F60">
         <v>26</v>
       </c>
-      <c r="G60">
-        <v>7</v>
-      </c>
       <c r="H60" t="s">
         <v>16</v>
       </c>
@@ -6075,9 +6031,6 @@
       <c r="F61">
         <v>17</v>
       </c>
-      <c r="G61">
-        <v>13</v>
-      </c>
       <c r="H61" t="s">
         <v>16</v>
       </c>
@@ -6251,9 +6204,6 @@
       <c r="F65">
         <v>21</v>
       </c>
-      <c r="G65">
-        <v>7</v>
-      </c>
       <c r="H65" t="s">
         <v>23</v>
       </c>
@@ -6471,9 +6421,6 @@
       <c r="F70">
         <v>21</v>
       </c>
-      <c r="G70">
-        <v>8</v>
-      </c>
       <c r="H70" t="s">
         <v>23</v>
       </c>
@@ -6647,9 +6594,6 @@
       <c r="F74">
         <v>18</v>
       </c>
-      <c r="G74">
-        <v>13</v>
-      </c>
       <c r="H74" t="s">
         <v>23</v>
       </c>
@@ -6735,9 +6679,6 @@
       <c r="F76">
         <v>11</v>
       </c>
-      <c r="G76">
-        <v>7</v>
-      </c>
       <c r="H76" t="s">
         <v>23</v>
       </c>
@@ -6955,9 +6896,6 @@
       <c r="F81">
         <v>22</v>
       </c>
-      <c r="G81">
-        <v>13</v>
-      </c>
       <c r="H81" t="s">
         <v>16</v>
       </c>
@@ -7043,9 +6981,6 @@
       <c r="F83">
         <v>16</v>
       </c>
-      <c r="G83">
-        <v>9</v>
-      </c>
       <c r="H83" t="s">
         <v>16</v>
       </c>
@@ -7263,9 +7198,6 @@
       <c r="F88">
         <v>19</v>
       </c>
-      <c r="G88">
-        <v>7</v>
-      </c>
       <c r="H88" t="s">
         <v>23</v>
       </c>
@@ -7483,9 +7415,6 @@
       <c r="F93">
         <v>19</v>
       </c>
-      <c r="G93">
-        <v>13</v>
-      </c>
       <c r="H93" t="s">
         <v>16</v>
       </c>
@@ -7571,9 +7500,6 @@
       <c r="F95">
         <v>21</v>
       </c>
-      <c r="G95">
-        <v>9</v>
-      </c>
       <c r="H95" t="s">
         <v>23</v>
       </c>
@@ -7791,9 +7717,6 @@
       <c r="F100">
         <v>18</v>
       </c>
-      <c r="G100">
-        <v>8</v>
-      </c>
       <c r="H100" t="s">
         <v>23</v>
       </c>
@@ -7835,9 +7758,6 @@
       <c r="F101">
         <v>16</v>
       </c>
-      <c r="G101">
-        <v>13</v>
-      </c>
       <c r="H101" t="s">
         <v>16</v>
       </c>
@@ -7879,9 +7799,6 @@
       <c r="F102">
         <v>17</v>
       </c>
-      <c r="G102">
-        <v>13</v>
-      </c>
       <c r="H102" t="s">
         <v>16</v>
       </c>
@@ -7967,9 +7884,6 @@
       <c r="F104">
         <v>20</v>
       </c>
-      <c r="G104">
-        <v>9</v>
-      </c>
       <c r="H104" t="s">
         <v>16</v>
       </c>
@@ -8055,9 +7969,6 @@
       <c r="F106">
         <v>20</v>
       </c>
-      <c r="G106">
-        <v>13</v>
-      </c>
       <c r="H106" t="s">
         <v>16</v>
       </c>
@@ -8275,9 +8186,6 @@
       <c r="F111">
         <v>19</v>
       </c>
-      <c r="G111">
-        <v>7</v>
-      </c>
       <c r="H111" t="s">
         <v>16</v>
       </c>
@@ -8495,9 +8403,6 @@
       <c r="F116">
         <v>21</v>
       </c>
-      <c r="G116">
-        <v>9</v>
-      </c>
       <c r="H116" t="s">
         <v>23</v>
       </c>
@@ -8539,9 +8444,6 @@
       <c r="F117">
         <v>12</v>
       </c>
-      <c r="G117">
-        <v>13</v>
-      </c>
       <c r="H117" t="s">
         <v>16</v>
       </c>
@@ -8627,9 +8529,6 @@
       <c r="F119">
         <v>12</v>
       </c>
-      <c r="G119">
-        <v>8</v>
-      </c>
       <c r="H119" t="s">
         <v>16</v>
       </c>
@@ -8715,9 +8614,6 @@
       <c r="F121">
         <v>10</v>
       </c>
-      <c r="G121">
-        <v>9</v>
-      </c>
       <c r="H121" t="s">
         <v>16</v>
       </c>
@@ -8803,9 +8699,6 @@
       <c r="F123">
         <v>19</v>
       </c>
-      <c r="G123">
-        <v>9</v>
-      </c>
       <c r="H123" t="s">
         <v>16</v>
       </c>
@@ -9023,9 +8916,6 @@
       <c r="F128">
         <v>17</v>
       </c>
-      <c r="G128">
-        <v>7</v>
-      </c>
       <c r="H128" t="s">
         <v>16</v>
       </c>
@@ -9067,9 +8957,6 @@
       <c r="F129">
         <v>12</v>
       </c>
-      <c r="G129">
-        <v>13</v>
-      </c>
       <c r="H129" t="s">
         <v>16</v>
       </c>
@@ -9111,9 +8998,6 @@
       <c r="F130">
         <v>18</v>
       </c>
-      <c r="G130">
-        <v>13</v>
-      </c>
       <c r="H130" t="s">
         <v>23</v>
       </c>
@@ -9199,9 +9083,6 @@
       <c r="F132">
         <v>17</v>
       </c>
-      <c r="G132">
-        <v>13</v>
-      </c>
       <c r="H132" t="s">
         <v>16</v>
       </c>
@@ -9463,9 +9344,6 @@
       <c r="F138">
         <v>12</v>
       </c>
-      <c r="G138">
-        <v>9</v>
-      </c>
       <c r="H138" t="s">
         <v>16</v>
       </c>
@@ -9639,9 +9517,6 @@
       <c r="F142">
         <v>24</v>
       </c>
-      <c r="G142">
-        <v>9</v>
-      </c>
       <c r="H142" t="s">
         <v>23</v>
       </c>
@@ -9684,7 +9559,7 @@
         <v>17</v>
       </c>
       <c r="G143">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H143" t="s">
         <v>16</v>
@@ -10079,9 +9954,6 @@
       <c r="F152">
         <v>16</v>
       </c>
-      <c r="G152">
-        <v>13</v>
-      </c>
       <c r="H152" t="s">
         <v>16</v>
       </c>
@@ -10255,9 +10127,6 @@
       <c r="F156">
         <v>17</v>
       </c>
-      <c r="G156">
-        <v>9</v>
-      </c>
       <c r="H156" t="s">
         <v>23</v>
       </c>
@@ -10299,9 +10168,6 @@
       <c r="F157">
         <v>16</v>
       </c>
-      <c r="G157">
-        <v>13</v>
-      </c>
       <c r="H157" t="s">
         <v>16</v>
       </c>
@@ -10431,9 +10297,6 @@
       <c r="F160">
         <v>18</v>
       </c>
-      <c r="G160">
-        <v>9</v>
-      </c>
       <c r="H160" t="s">
         <v>16</v>
       </c>
@@ -10475,9 +10338,6 @@
       <c r="F161">
         <v>14</v>
       </c>
-      <c r="G161">
-        <v>9</v>
-      </c>
       <c r="H161" t="s">
         <v>23</v>
       </c>
@@ -10519,9 +10379,6 @@
       <c r="F162">
         <v>15</v>
       </c>
-      <c r="G162">
-        <v>8</v>
-      </c>
       <c r="H162" t="s">
         <v>16</v>
       </c>
@@ -10783,9 +10640,6 @@
       <c r="F168">
         <v>15</v>
       </c>
-      <c r="G168">
-        <v>13</v>
-      </c>
       <c r="H168" t="s">
         <v>16</v>
       </c>
@@ -10827,9 +10681,6 @@
       <c r="F169">
         <v>19</v>
       </c>
-      <c r="G169">
-        <v>9</v>
-      </c>
       <c r="H169" t="s">
         <v>16</v>
       </c>
@@ -10871,9 +10722,6 @@
       <c r="F170">
         <v>23</v>
       </c>
-      <c r="G170">
-        <v>9</v>
-      </c>
       <c r="H170" t="s">
         <v>23</v>
       </c>
@@ -11048,7 +10896,7 @@
         <v>19</v>
       </c>
       <c r="G174">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H174" t="s">
         <v>16</v>
@@ -11179,9 +11027,6 @@
       <c r="F177">
         <v>17</v>
       </c>
-      <c r="G177">
-        <v>8</v>
-      </c>
       <c r="H177" t="s">
         <v>23</v>
       </c>
@@ -11267,9 +11112,6 @@
       <c r="F179">
         <v>19</v>
       </c>
-      <c r="G179">
-        <v>8</v>
-      </c>
       <c r="H179" t="s">
         <v>16</v>
       </c>
@@ -11399,9 +11241,6 @@
       <c r="F182">
         <v>17</v>
       </c>
-      <c r="G182">
-        <v>9</v>
-      </c>
       <c r="H182" t="s">
         <v>16</v>
       </c>
@@ -11531,9 +11370,6 @@
       <c r="F185">
         <v>16</v>
       </c>
-      <c r="G185">
-        <v>13</v>
-      </c>
       <c r="H185" t="s">
         <v>16</v>
       </c>
@@ -11575,9 +11411,6 @@
       <c r="F186">
         <v>16</v>
       </c>
-      <c r="G186">
-        <v>13</v>
-      </c>
       <c r="H186" t="s">
         <v>16</v>
       </c>
@@ -12103,9 +11936,6 @@
       <c r="F198">
         <v>15</v>
       </c>
-      <c r="G198">
-        <v>13</v>
-      </c>
       <c r="H198" t="s">
         <v>23</v>
       </c>
@@ -12147,9 +11977,6 @@
       <c r="F199">
         <v>17</v>
       </c>
-      <c r="G199">
-        <v>9</v>
-      </c>
       <c r="H199" t="s">
         <v>16</v>
       </c>
@@ -12191,9 +12018,6 @@
       <c r="F200">
         <v>17</v>
       </c>
-      <c r="G200">
-        <v>8</v>
-      </c>
       <c r="H200" t="s">
         <v>16</v>
       </c>
@@ -12235,9 +12059,6 @@
       <c r="F201">
         <v>23</v>
       </c>
-      <c r="G201">
-        <v>7</v>
-      </c>
       <c r="H201" t="s">
         <v>16</v>
       </c>
@@ -12323,9 +12144,6 @@
       <c r="F203">
         <v>13</v>
       </c>
-      <c r="G203">
-        <v>7</v>
-      </c>
       <c r="H203" t="s">
         <v>16</v>
       </c>
@@ -12411,9 +12229,6 @@
       <c r="F205">
         <v>12</v>
       </c>
-      <c r="G205">
-        <v>13</v>
-      </c>
       <c r="H205" t="s">
         <v>16</v>
       </c>
@@ -12455,9 +12270,6 @@
       <c r="F206">
         <v>13</v>
       </c>
-      <c r="G206">
-        <v>13</v>
-      </c>
       <c r="H206" t="s">
         <v>23</v>
       </c>
@@ -12499,9 +12311,6 @@
       <c r="F207">
         <v>16</v>
       </c>
-      <c r="G207">
-        <v>13</v>
-      </c>
       <c r="H207" t="s">
         <v>16</v>
       </c>
@@ -12675,9 +12484,6 @@
       <c r="F211">
         <v>12</v>
       </c>
-      <c r="G211">
-        <v>7</v>
-      </c>
       <c r="H211" t="s">
         <v>16</v>
       </c>
@@ -12719,9 +12525,6 @@
       <c r="F212">
         <v>18</v>
       </c>
-      <c r="G212">
-        <v>8</v>
-      </c>
       <c r="H212" t="s">
         <v>16</v>
       </c>
@@ -12939,9 +12742,6 @@
       <c r="F217">
         <v>22</v>
       </c>
-      <c r="G217">
-        <v>9</v>
-      </c>
       <c r="H217" t="s">
         <v>23</v>
       </c>
@@ -12983,9 +12783,6 @@
       <c r="F218">
         <v>24</v>
       </c>
-      <c r="G218">
-        <v>9</v>
-      </c>
       <c r="H218" t="s">
         <v>16</v>
       </c>
@@ -13027,9 +12824,6 @@
       <c r="F219">
         <v>21</v>
       </c>
-      <c r="G219">
-        <v>8</v>
-      </c>
       <c r="H219" t="s">
         <v>23</v>
       </c>
@@ -13071,9 +12865,6 @@
       <c r="F220">
         <v>11</v>
       </c>
-      <c r="G220">
-        <v>13</v>
-      </c>
       <c r="H220" t="s">
         <v>16</v>
       </c>
@@ -13335,9 +13126,6 @@
       <c r="F226">
         <v>17</v>
       </c>
-      <c r="G226">
-        <v>13</v>
-      </c>
       <c r="H226" t="s">
         <v>16</v>
       </c>
@@ -13379,9 +13167,6 @@
       <c r="F227">
         <v>13</v>
       </c>
-      <c r="G227">
-        <v>9</v>
-      </c>
       <c r="H227" t="s">
         <v>16</v>
       </c>
@@ -13467,9 +13252,6 @@
       <c r="F229">
         <v>20</v>
       </c>
-      <c r="G229">
-        <v>13</v>
-      </c>
       <c r="H229" t="s">
         <v>16</v>
       </c>
@@ -13599,9 +13381,6 @@
       <c r="F232">
         <v>16</v>
       </c>
-      <c r="G232">
-        <v>7</v>
-      </c>
       <c r="H232" t="s">
         <v>16</v>
       </c>
@@ -13731,9 +13510,6 @@
       <c r="F235">
         <v>14</v>
       </c>
-      <c r="G235">
-        <v>13</v>
-      </c>
       <c r="H235" t="s">
         <v>16</v>
       </c>
@@ -13776,7 +13552,7 @@
         <v>18</v>
       </c>
       <c r="G236">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H236" t="s">
         <v>23</v>
@@ -13951,9 +13727,6 @@
       <c r="F240">
         <v>19</v>
       </c>
-      <c r="G240">
-        <v>8</v>
-      </c>
       <c r="H240" t="s">
         <v>23</v>
       </c>
@@ -14039,9 +13812,6 @@
       <c r="F242">
         <v>18</v>
       </c>
-      <c r="G242">
-        <v>8</v>
-      </c>
       <c r="H242" t="s">
         <v>16</v>
       </c>
@@ -14347,9 +14117,6 @@
       <c r="F249">
         <v>22</v>
       </c>
-      <c r="G249">
-        <v>9</v>
-      </c>
       <c r="H249" t="s">
         <v>23</v>
       </c>
@@ -14435,9 +14202,6 @@
       <c r="F251">
         <v>10</v>
       </c>
-      <c r="G251">
-        <v>9</v>
-      </c>
       <c r="H251" t="s">
         <v>16</v>
       </c>
@@ -14479,9 +14243,6 @@
       <c r="F252">
         <v>17</v>
       </c>
-      <c r="G252">
-        <v>13</v>
-      </c>
       <c r="H252" t="s">
         <v>16</v>
       </c>
@@ -14567,9 +14328,6 @@
       <c r="F254">
         <v>15</v>
       </c>
-      <c r="G254">
-        <v>13</v>
-      </c>
       <c r="H254" t="s">
         <v>16</v>
       </c>
@@ -14655,9 +14413,6 @@
       <c r="F256">
         <v>10</v>
       </c>
-      <c r="G256">
-        <v>13</v>
-      </c>
       <c r="H256" t="s">
         <v>16</v>
       </c>
@@ -14743,9 +14498,6 @@
       <c r="F258">
         <v>22</v>
       </c>
-      <c r="G258">
-        <v>9</v>
-      </c>
       <c r="H258" t="s">
         <v>16</v>
       </c>
@@ -15139,9 +14891,6 @@
       <c r="F267">
         <v>10</v>
       </c>
-      <c r="G267">
-        <v>13</v>
-      </c>
       <c r="H267" t="s">
         <v>23</v>
       </c>
@@ -15183,9 +14932,6 @@
       <c r="F268">
         <v>13</v>
       </c>
-      <c r="G268">
-        <v>13</v>
-      </c>
       <c r="H268" t="s">
         <v>16</v>
       </c>
@@ -15271,9 +15017,6 @@
       <c r="F270">
         <v>18</v>
       </c>
-      <c r="G270">
-        <v>13</v>
-      </c>
       <c r="H270" t="s">
         <v>16</v>
       </c>
@@ -15315,9 +15058,6 @@
       <c r="F271">
         <v>10</v>
       </c>
-      <c r="G271">
-        <v>13</v>
-      </c>
       <c r="H271" t="s">
         <v>16</v>
       </c>
@@ -15535,9 +15275,6 @@
       <c r="F276">
         <v>11</v>
       </c>
-      <c r="G276">
-        <v>13</v>
-      </c>
       <c r="H276" t="s">
         <v>16</v>
       </c>
@@ -15579,9 +15316,6 @@
       <c r="F277">
         <v>26</v>
       </c>
-      <c r="G277">
-        <v>9</v>
-      </c>
       <c r="H277" t="s">
         <v>16</v>
       </c>
@@ -15711,9 +15445,6 @@
       <c r="F280">
         <v>17</v>
       </c>
-      <c r="G280">
-        <v>9</v>
-      </c>
       <c r="H280" t="s">
         <v>23</v>
       </c>
@@ -15843,9 +15574,6 @@
       <c r="F283">
         <v>17</v>
       </c>
-      <c r="G283">
-        <v>9</v>
-      </c>
       <c r="H283" t="s">
         <v>16</v>
       </c>
@@ -15931,9 +15659,6 @@
       <c r="F285">
         <v>15</v>
       </c>
-      <c r="G285">
-        <v>13</v>
-      </c>
       <c r="H285" t="s">
         <v>16</v>
       </c>
@@ -15975,9 +15700,6 @@
       <c r="F286">
         <v>13</v>
       </c>
-      <c r="G286">
-        <v>9</v>
-      </c>
       <c r="H286" t="s">
         <v>16</v>
       </c>
@@ -16063,9 +15785,6 @@
       <c r="F288">
         <v>14</v>
       </c>
-      <c r="G288">
-        <v>8</v>
-      </c>
       <c r="H288" t="s">
         <v>16</v>
       </c>
@@ -16151,9 +15870,6 @@
       <c r="F290">
         <v>15</v>
       </c>
-      <c r="G290">
-        <v>9</v>
-      </c>
       <c r="H290" t="s">
         <v>23</v>
       </c>
@@ -16459,9 +16175,6 @@
       <c r="F297">
         <v>20</v>
       </c>
-      <c r="G297">
-        <v>8</v>
-      </c>
       <c r="H297" t="s">
         <v>23</v>
       </c>
@@ -16547,9 +16260,6 @@
       <c r="F299">
         <v>23</v>
       </c>
-      <c r="G299">
-        <v>7</v>
-      </c>
       <c r="H299" t="s">
         <v>23</v>
       </c>
@@ -16591,9 +16301,6 @@
       <c r="F300">
         <v>23</v>
       </c>
-      <c r="G300">
-        <v>8</v>
-      </c>
       <c r="H300" t="s">
         <v>23</v>
       </c>
@@ -16635,9 +16342,6 @@
       <c r="F301">
         <v>16</v>
       </c>
-      <c r="G301">
-        <v>7</v>
-      </c>
       <c r="H301" t="s">
         <v>16</v>
       </c>
@@ -16723,9 +16427,6 @@
       <c r="F303">
         <v>12</v>
       </c>
-      <c r="G303">
-        <v>13</v>
-      </c>
       <c r="H303" t="s">
         <v>16</v>
       </c>
@@ -16767,9 +16468,6 @@
       <c r="F304">
         <v>18</v>
       </c>
-      <c r="G304">
-        <v>13</v>
-      </c>
       <c r="H304" t="s">
         <v>16</v>
       </c>
@@ -16811,9 +16509,6 @@
       <c r="F305">
         <v>16</v>
       </c>
-      <c r="G305">
-        <v>13</v>
-      </c>
       <c r="H305" t="s">
         <v>16</v>
       </c>
@@ -16899,9 +16594,6 @@
       <c r="F307">
         <v>21</v>
       </c>
-      <c r="G307">
-        <v>13</v>
-      </c>
       <c r="H307" t="s">
         <v>16</v>
       </c>
@@ -16943,9 +16635,6 @@
       <c r="F308">
         <v>12</v>
       </c>
-      <c r="G308">
-        <v>13</v>
-      </c>
       <c r="H308" t="s">
         <v>16</v>
       </c>
@@ -17031,9 +16720,6 @@
       <c r="F310">
         <v>13</v>
       </c>
-      <c r="G310">
-        <v>13</v>
-      </c>
       <c r="H310" t="s">
         <v>16</v>
       </c>
@@ -17075,9 +16761,6 @@
       <c r="F311">
         <v>12</v>
       </c>
-      <c r="G311">
-        <v>8</v>
-      </c>
       <c r="H311" t="s">
         <v>16</v>
       </c>
@@ -17119,9 +16802,6 @@
       <c r="F312">
         <v>18</v>
       </c>
-      <c r="G312">
-        <v>13</v>
-      </c>
       <c r="H312" t="s">
         <v>16</v>
       </c>
@@ -17559,9 +17239,6 @@
       <c r="F322">
         <v>17</v>
       </c>
-      <c r="G322">
-        <v>7</v>
-      </c>
       <c r="H322" t="s">
         <v>23</v>
       </c>
@@ -17603,9 +17280,6 @@
       <c r="F323">
         <v>12</v>
       </c>
-      <c r="G323">
-        <v>9</v>
-      </c>
       <c r="H323" t="s">
         <v>16</v>
       </c>
@@ -17647,9 +17321,6 @@
       <c r="F324">
         <v>15</v>
       </c>
-      <c r="G324">
-        <v>8</v>
-      </c>
       <c r="H324" t="s">
         <v>16</v>
       </c>
@@ -17735,9 +17406,6 @@
       <c r="F326">
         <v>24</v>
       </c>
-      <c r="G326">
-        <v>13</v>
-      </c>
       <c r="H326" t="s">
         <v>16</v>
       </c>
@@ -17867,9 +17535,6 @@
       <c r="F329">
         <v>17</v>
       </c>
-      <c r="G329">
-        <v>8</v>
-      </c>
       <c r="H329" t="s">
         <v>16</v>
       </c>
@@ -17911,9 +17576,6 @@
       <c r="F330">
         <v>20</v>
       </c>
-      <c r="G330">
-        <v>9</v>
-      </c>
       <c r="H330" t="s">
         <v>16</v>
       </c>
@@ -17999,9 +17661,6 @@
       <c r="F332">
         <v>18</v>
       </c>
-      <c r="G332">
-        <v>13</v>
-      </c>
       <c r="H332" t="s">
         <v>16</v>
       </c>
@@ -18043,9 +17702,6 @@
       <c r="F333">
         <v>10</v>
       </c>
-      <c r="G333">
-        <v>8</v>
-      </c>
       <c r="H333" t="s">
         <v>16</v>
       </c>
@@ -18131,9 +17787,6 @@
       <c r="F335">
         <v>17</v>
       </c>
-      <c r="G335">
-        <v>9</v>
-      </c>
       <c r="H335" t="s">
         <v>16</v>
       </c>
@@ -18219,9 +17872,6 @@
       <c r="F337">
         <v>18</v>
       </c>
-      <c r="G337">
-        <v>9</v>
-      </c>
       <c r="H337" t="s">
         <v>16</v>
       </c>
@@ -18395,9 +18045,6 @@
       <c r="F341">
         <v>15</v>
       </c>
-      <c r="G341">
-        <v>13</v>
-      </c>
       <c r="H341" t="s">
         <v>16</v>
       </c>
@@ -18439,9 +18086,6 @@
       <c r="F342">
         <v>17</v>
       </c>
-      <c r="G342">
-        <v>13</v>
-      </c>
       <c r="H342" t="s">
         <v>23</v>
       </c>
@@ -18571,9 +18215,6 @@
       <c r="F345">
         <v>24</v>
       </c>
-      <c r="G345">
-        <v>5</v>
-      </c>
       <c r="H345" t="s">
         <v>16</v>
       </c>
@@ -18659,9 +18300,6 @@
       <c r="F347">
         <v>19</v>
       </c>
-      <c r="G347">
-        <v>13</v>
-      </c>
       <c r="H347" t="s">
         <v>23</v>
       </c>
@@ -18747,9 +18385,6 @@
       <c r="F349">
         <v>21</v>
       </c>
-      <c r="G349">
-        <v>8</v>
-      </c>
       <c r="H349" t="s">
         <v>16</v>
       </c>
@@ -18835,9 +18470,6 @@
       <c r="F351">
         <v>19</v>
       </c>
-      <c r="G351">
-        <v>9</v>
-      </c>
       <c r="H351" t="s">
         <v>23</v>
       </c>
@@ -19011,9 +18643,6 @@
       <c r="F355">
         <v>14</v>
       </c>
-      <c r="G355">
-        <v>13</v>
-      </c>
       <c r="H355" t="s">
         <v>23</v>
       </c>
@@ -19055,9 +18684,6 @@
       <c r="F356">
         <v>20</v>
       </c>
-      <c r="G356">
-        <v>9</v>
-      </c>
       <c r="H356" t="s">
         <v>16</v>
       </c>
@@ -19099,9 +18725,6 @@
       <c r="F357">
         <v>22</v>
       </c>
-      <c r="G357">
-        <v>9</v>
-      </c>
       <c r="H357" t="s">
         <v>23</v>
       </c>
@@ -19143,9 +18766,6 @@
       <c r="F358">
         <v>10</v>
       </c>
-      <c r="G358">
-        <v>13</v>
-      </c>
       <c r="H358" t="s">
         <v>23</v>
       </c>
@@ -19187,9 +18807,6 @@
       <c r="F359">
         <v>17</v>
       </c>
-      <c r="G359">
-        <v>8</v>
-      </c>
       <c r="H359" t="s">
         <v>23</v>
       </c>
@@ -19275,9 +18892,6 @@
       <c r="F361">
         <v>18</v>
       </c>
-      <c r="G361">
-        <v>9</v>
-      </c>
       <c r="H361" t="s">
         <v>23</v>
       </c>
@@ -19319,9 +18933,6 @@
       <c r="F362">
         <v>18</v>
       </c>
-      <c r="G362">
-        <v>13</v>
-      </c>
       <c r="H362" t="s">
         <v>16</v>
       </c>
@@ -19363,9 +18974,6 @@
       <c r="F363">
         <v>13</v>
       </c>
-      <c r="G363">
-        <v>13</v>
-      </c>
       <c r="H363" t="s">
         <v>16</v>
       </c>
@@ -19407,9 +19015,6 @@
       <c r="F364">
         <v>18</v>
       </c>
-      <c r="G364">
-        <v>5</v>
-      </c>
       <c r="H364" t="s">
         <v>23</v>
       </c>
@@ -19539,9 +19144,6 @@
       <c r="F367">
         <v>19</v>
       </c>
-      <c r="G367">
-        <v>7</v>
-      </c>
       <c r="H367" t="s">
         <v>23</v>
       </c>
@@ -19583,9 +19185,6 @@
       <c r="F368">
         <v>14</v>
       </c>
-      <c r="G368">
-        <v>13</v>
-      </c>
       <c r="H368" t="s">
         <v>23</v>
       </c>
@@ -19627,9 +19226,6 @@
       <c r="F369">
         <v>20</v>
       </c>
-      <c r="G369">
-        <v>5</v>
-      </c>
       <c r="H369" t="s">
         <v>23</v>
       </c>
@@ -19671,9 +19267,6 @@
       <c r="F370">
         <v>13</v>
       </c>
-      <c r="G370">
-        <v>13</v>
-      </c>
       <c r="H370" t="s">
         <v>16</v>
       </c>
@@ -19715,9 +19308,6 @@
       <c r="F371">
         <v>12</v>
       </c>
-      <c r="G371">
-        <v>13</v>
-      </c>
       <c r="H371" t="s">
         <v>16</v>
       </c>
@@ -19759,9 +19349,6 @@
       <c r="F372">
         <v>17</v>
       </c>
-      <c r="G372">
-        <v>5</v>
-      </c>
       <c r="H372" t="s">
         <v>23</v>
       </c>
@@ -19891,9 +19478,6 @@
       <c r="F375">
         <v>19</v>
       </c>
-      <c r="G375">
-        <v>7</v>
-      </c>
       <c r="H375" t="s">
         <v>23</v>
       </c>
@@ -19935,9 +19519,6 @@
       <c r="F376">
         <v>21</v>
       </c>
-      <c r="G376">
-        <v>13</v>
-      </c>
       <c r="H376" t="s">
         <v>23</v>
       </c>
@@ -20243,9 +19824,6 @@
       <c r="F383">
         <v>17</v>
       </c>
-      <c r="G383">
-        <v>13</v>
-      </c>
       <c r="H383" t="s">
         <v>16</v>
       </c>
@@ -20331,9 +19909,6 @@
       <c r="F385">
         <v>10</v>
       </c>
-      <c r="G385">
-        <v>7</v>
-      </c>
       <c r="H385" t="s">
         <v>16</v>
       </c>
@@ -20419,9 +19994,6 @@
       <c r="F387">
         <v>13</v>
       </c>
-      <c r="G387">
-        <v>13</v>
-      </c>
       <c r="H387" t="s">
         <v>16</v>
       </c>
@@ -20463,9 +20035,6 @@
       <c r="F388">
         <v>12</v>
       </c>
-      <c r="G388">
-        <v>13</v>
-      </c>
       <c r="H388" t="s">
         <v>16</v>
       </c>
@@ -20683,9 +20252,6 @@
       <c r="F393">
         <v>25</v>
       </c>
-      <c r="G393">
-        <v>9</v>
-      </c>
       <c r="H393" t="s">
         <v>23</v>
       </c>
@@ -20771,9 +20337,6 @@
       <c r="F395">
         <v>18</v>
       </c>
-      <c r="G395">
-        <v>9</v>
-      </c>
       <c r="H395" t="s">
         <v>23</v>
       </c>
@@ -20815,9 +20378,6 @@
       <c r="F396">
         <v>22</v>
       </c>
-      <c r="G396">
-        <v>9</v>
-      </c>
       <c r="H396" t="s">
         <v>16</v>
       </c>
@@ -21079,9 +20639,6 @@
       <c r="F402">
         <v>20</v>
       </c>
-      <c r="G402">
-        <v>7</v>
-      </c>
       <c r="H402" t="s">
         <v>23</v>
       </c>
@@ -21167,9 +20724,6 @@
       <c r="F404">
         <v>14</v>
       </c>
-      <c r="G404">
-        <v>7</v>
-      </c>
       <c r="H404" t="s">
         <v>23</v>
       </c>
@@ -21343,9 +20897,6 @@
       <c r="F408">
         <v>15</v>
       </c>
-      <c r="G408">
-        <v>13</v>
-      </c>
       <c r="H408" t="s">
         <v>23</v>
       </c>
@@ -21431,9 +20982,6 @@
       <c r="F410">
         <v>16</v>
       </c>
-      <c r="G410">
-        <v>9</v>
-      </c>
       <c r="H410" t="s">
         <v>23</v>
       </c>
@@ -21519,9 +21067,6 @@
       <c r="F412">
         <v>15</v>
       </c>
-      <c r="G412">
-        <v>13</v>
-      </c>
       <c r="H412" t="s">
         <v>23</v>
       </c>
@@ -21563,9 +21108,6 @@
       <c r="F413">
         <v>22</v>
       </c>
-      <c r="G413">
-        <v>9</v>
-      </c>
       <c r="H413" t="s">
         <v>23</v>
       </c>
@@ -21651,9 +21193,6 @@
       <c r="F415">
         <v>11</v>
       </c>
-      <c r="G415">
-        <v>13</v>
-      </c>
       <c r="H415" t="s">
         <v>16</v>
       </c>
@@ -21827,9 +21366,6 @@
       <c r="F419">
         <v>16</v>
       </c>
-      <c r="G419">
-        <v>7</v>
-      </c>
       <c r="H419" t="s">
         <v>16</v>
       </c>
@@ -21871,9 +21407,6 @@
       <c r="F420">
         <v>13</v>
       </c>
-      <c r="G420">
-        <v>13</v>
-      </c>
       <c r="H420" t="s">
         <v>16</v>
       </c>
@@ -22091,9 +21624,6 @@
       <c r="F425">
         <v>19</v>
       </c>
-      <c r="G425">
-        <v>13</v>
-      </c>
       <c r="H425" t="s">
         <v>16</v>
       </c>
@@ -22179,9 +21709,6 @@
       <c r="F427">
         <v>19</v>
       </c>
-      <c r="G427">
-        <v>11</v>
-      </c>
       <c r="H427" t="s">
         <v>16</v>
       </c>
@@ -22267,9 +21794,6 @@
       <c r="F429">
         <v>21</v>
       </c>
-      <c r="G429">
-        <v>7</v>
-      </c>
       <c r="H429" t="s">
         <v>16</v>
       </c>
@@ -22311,9 +21835,6 @@
       <c r="F430">
         <v>18</v>
       </c>
-      <c r="G430">
-        <v>8</v>
-      </c>
       <c r="H430" t="s">
         <v>16</v>
       </c>
@@ -22355,9 +21876,6 @@
       <c r="F431">
         <v>20</v>
       </c>
-      <c r="G431">
-        <v>13</v>
-      </c>
       <c r="H431" t="s">
         <v>16</v>
       </c>
@@ -22443,9 +21961,6 @@
       <c r="F433">
         <v>13</v>
       </c>
-      <c r="G433">
-        <v>13</v>
-      </c>
       <c r="H433" t="s">
         <v>16</v>
       </c>
@@ -22487,9 +22002,6 @@
       <c r="F434">
         <v>19</v>
       </c>
-      <c r="G434">
-        <v>13</v>
-      </c>
       <c r="H434" t="s">
         <v>16</v>
       </c>
@@ -22575,9 +22087,6 @@
       <c r="F436">
         <v>15</v>
       </c>
-      <c r="G436">
-        <v>8</v>
-      </c>
       <c r="H436" t="s">
         <v>16</v>
       </c>
@@ -22619,9 +22128,6 @@
       <c r="F437">
         <v>13</v>
       </c>
-      <c r="G437">
-        <v>7</v>
-      </c>
       <c r="H437" t="s">
         <v>23</v>
       </c>
@@ -22751,9 +22257,6 @@
       <c r="F440">
         <v>17</v>
       </c>
-      <c r="G440">
-        <v>8</v>
-      </c>
       <c r="H440" t="s">
         <v>16</v>
       </c>
@@ -23015,9 +22518,6 @@
       <c r="F446">
         <v>12</v>
       </c>
-      <c r="G446">
-        <v>8</v>
-      </c>
       <c r="H446" t="s">
         <v>23</v>
       </c>
@@ -23103,9 +22603,6 @@
       <c r="F448">
         <v>14</v>
       </c>
-      <c r="G448">
-        <v>13</v>
-      </c>
       <c r="H448" t="s">
         <v>16</v>
       </c>
@@ -23191,9 +22688,6 @@
       <c r="F450">
         <v>17</v>
       </c>
-      <c r="G450">
-        <v>13</v>
-      </c>
       <c r="H450" t="s">
         <v>16</v>
       </c>
@@ -23367,9 +22861,6 @@
       <c r="F454">
         <v>18</v>
       </c>
-      <c r="G454">
-        <v>9</v>
-      </c>
       <c r="H454" t="s">
         <v>23</v>
       </c>
@@ -23411,9 +22902,6 @@
       <c r="F455">
         <v>19</v>
       </c>
-      <c r="G455">
-        <v>8</v>
-      </c>
       <c r="H455" t="s">
         <v>16</v>
       </c>
@@ -23587,9 +23075,6 @@
       <c r="F459">
         <v>12</v>
       </c>
-      <c r="G459">
-        <v>13</v>
-      </c>
       <c r="H459" t="s">
         <v>16</v>
       </c>
@@ -23719,9 +23204,6 @@
       <c r="F462">
         <v>13</v>
       </c>
-      <c r="G462">
-        <v>7</v>
-      </c>
       <c r="H462" t="s">
         <v>16</v>
       </c>
@@ -23763,9 +23245,6 @@
       <c r="F463">
         <v>16</v>
       </c>
-      <c r="G463">
-        <v>9</v>
-      </c>
       <c r="H463" t="s">
         <v>16</v>
       </c>
@@ -23851,9 +23330,6 @@
       <c r="F465">
         <v>22</v>
       </c>
-      <c r="G465">
-        <v>8</v>
-      </c>
       <c r="H465" t="s">
         <v>16</v>
       </c>
@@ -24159,9 +23635,6 @@
       <c r="F472">
         <v>18</v>
       </c>
-      <c r="G472">
-        <v>13</v>
-      </c>
       <c r="H472" t="s">
         <v>16</v>
       </c>
@@ -24467,9 +23940,6 @@
       <c r="F479">
         <v>10</v>
       </c>
-      <c r="G479">
-        <v>11</v>
-      </c>
       <c r="H479" t="s">
         <v>23</v>
       </c>
@@ -24599,9 +24069,6 @@
       <c r="F482">
         <v>17</v>
       </c>
-      <c r="G482">
-        <v>9</v>
-      </c>
       <c r="H482" t="s">
         <v>16</v>
       </c>
@@ -24951,9 +24418,6 @@
       <c r="F490">
         <v>20</v>
       </c>
-      <c r="G490">
-        <v>9</v>
-      </c>
       <c r="H490" t="s">
         <v>23</v>
       </c>
@@ -25391,9 +24855,6 @@
       <c r="F500">
         <v>16</v>
       </c>
-      <c r="G500">
-        <v>13</v>
-      </c>
       <c r="H500" t="s">
         <v>16</v>
       </c>
@@ -25435,9 +24896,6 @@
       <c r="F501">
         <v>23</v>
       </c>
-      <c r="G501">
-        <v>9</v>
-      </c>
       <c r="H501" t="s">
         <v>16</v>
       </c>
@@ -25523,9 +24981,6 @@
       <c r="F503">
         <v>11</v>
       </c>
-      <c r="G503">
-        <v>13</v>
-      </c>
       <c r="H503" t="s">
         <v>16</v>
       </c>
@@ -25611,9 +25066,6 @@
       <c r="F505">
         <v>18</v>
       </c>
-      <c r="G505">
-        <v>7</v>
-      </c>
       <c r="H505" t="s">
         <v>23</v>
       </c>
@@ -25699,9 +25151,6 @@
       <c r="F507">
         <v>19</v>
       </c>
-      <c r="G507">
-        <v>9</v>
-      </c>
       <c r="H507" t="s">
         <v>23</v>
       </c>
@@ -25831,9 +25280,6 @@
       <c r="F510">
         <v>14</v>
       </c>
-      <c r="G510">
-        <v>7</v>
-      </c>
       <c r="H510" t="s">
         <v>16</v>
       </c>
@@ -25919,9 +25365,6 @@
       <c r="F512">
         <v>17</v>
       </c>
-      <c r="G512">
-        <v>9</v>
-      </c>
       <c r="H512" t="s">
         <v>23</v>
       </c>
@@ -26007,9 +25450,6 @@
       <c r="F514">
         <v>20</v>
       </c>
-      <c r="G514">
-        <v>13</v>
-      </c>
       <c r="H514" t="s">
         <v>16</v>
       </c>
@@ -26095,9 +25535,6 @@
       <c r="F516">
         <v>16</v>
       </c>
-      <c r="G516">
-        <v>13</v>
-      </c>
       <c r="H516" t="s">
         <v>16</v>
       </c>
@@ -26139,9 +25576,6 @@
       <c r="F517">
         <v>16</v>
       </c>
-      <c r="G517">
-        <v>7</v>
-      </c>
       <c r="H517" t="s">
         <v>16</v>
       </c>
@@ -26315,9 +25749,6 @@
       <c r="F521">
         <v>13</v>
       </c>
-      <c r="G521">
-        <v>7</v>
-      </c>
       <c r="H521" t="s">
         <v>16</v>
       </c>
@@ -26491,9 +25922,6 @@
       <c r="F525">
         <v>14</v>
       </c>
-      <c r="G525">
-        <v>13</v>
-      </c>
       <c r="H525" t="s">
         <v>16</v>
       </c>
@@ -26711,9 +26139,6 @@
       <c r="F530">
         <v>10</v>
       </c>
-      <c r="G530">
-        <v>7</v>
-      </c>
       <c r="H530" t="s">
         <v>23</v>
       </c>
@@ -26799,9 +26224,6 @@
       <c r="F532">
         <v>10</v>
       </c>
-      <c r="G532">
-        <v>13</v>
-      </c>
       <c r="H532" t="s">
         <v>16</v>
       </c>
@@ -26843,9 +26265,6 @@
       <c r="F533">
         <v>20</v>
       </c>
-      <c r="G533">
-        <v>7</v>
-      </c>
       <c r="H533" t="s">
         <v>23</v>
       </c>
@@ -27107,9 +26526,6 @@
       <c r="F539">
         <v>21</v>
       </c>
-      <c r="G539">
-        <v>11</v>
-      </c>
       <c r="H539" t="s">
         <v>16</v>
       </c>
@@ -27371,9 +26787,6 @@
       <c r="F545">
         <v>13</v>
       </c>
-      <c r="G545">
-        <v>13</v>
-      </c>
       <c r="H545" t="s">
         <v>16</v>
       </c>
@@ -27415,9 +26828,6 @@
       <c r="F546">
         <v>15</v>
       </c>
-      <c r="G546">
-        <v>13</v>
-      </c>
       <c r="H546" t="s">
         <v>23</v>
       </c>
@@ -27459,9 +26869,6 @@
       <c r="F547">
         <v>12</v>
       </c>
-      <c r="G547">
-        <v>13</v>
-      </c>
       <c r="H547" t="s">
         <v>16</v>
       </c>
@@ -27503,9 +26910,6 @@
       <c r="F548">
         <v>14</v>
       </c>
-      <c r="G548">
-        <v>13</v>
-      </c>
       <c r="H548" t="s">
         <v>23</v>
       </c>
@@ -27635,9 +27039,6 @@
       <c r="F551">
         <v>20</v>
       </c>
-      <c r="G551">
-        <v>7</v>
-      </c>
       <c r="H551" t="s">
         <v>23</v>
       </c>
@@ -27724,7 +27125,7 @@
         <v>15</v>
       </c>
       <c r="G553">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H553" t="s">
         <v>16</v>
@@ -27812,7 +27213,7 @@
         <v>12</v>
       </c>
       <c r="G555">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H555" t="s">
         <v>23</v>
@@ -28031,9 +27432,6 @@
       <c r="F560">
         <v>30</v>
       </c>
-      <c r="G560">
-        <v>8</v>
-      </c>
       <c r="H560" t="s">
         <v>23</v>
       </c>
@@ -28163,9 +27561,6 @@
       <c r="F563">
         <v>15</v>
       </c>
-      <c r="G563">
-        <v>9</v>
-      </c>
       <c r="H563" t="s">
         <v>16</v>
       </c>
@@ -28207,9 +27602,6 @@
       <c r="F564">
         <v>20</v>
       </c>
-      <c r="G564">
-        <v>8</v>
-      </c>
       <c r="H564" t="s">
         <v>23</v>
       </c>
@@ -28471,9 +27863,6 @@
       <c r="F570">
         <v>19</v>
       </c>
-      <c r="G570">
-        <v>13</v>
-      </c>
       <c r="H570" t="s">
         <v>16</v>
       </c>
@@ -28559,9 +27948,6 @@
       <c r="F572">
         <v>27</v>
       </c>
-      <c r="G572">
-        <v>8</v>
-      </c>
       <c r="H572" t="s">
         <v>16</v>
       </c>
@@ -28735,9 +28121,6 @@
       <c r="F576">
         <v>10</v>
       </c>
-      <c r="G576">
-        <v>13</v>
-      </c>
       <c r="H576" t="s">
         <v>16</v>
       </c>
@@ -28823,9 +28206,6 @@
       <c r="F578">
         <v>23</v>
       </c>
-      <c r="G578">
-        <v>9</v>
-      </c>
       <c r="H578" t="s">
         <v>16</v>
       </c>
@@ -28911,9 +28291,6 @@
       <c r="F580">
         <v>14</v>
       </c>
-      <c r="G580">
-        <v>13</v>
-      </c>
       <c r="H580" t="s">
         <v>23</v>
       </c>
@@ -28999,9 +28376,6 @@
       <c r="F582">
         <v>20</v>
       </c>
-      <c r="G582">
-        <v>13</v>
-      </c>
       <c r="H582" t="s">
         <v>16</v>
       </c>
@@ -29043,9 +28417,6 @@
       <c r="F583">
         <v>17</v>
       </c>
-      <c r="G583">
-        <v>8</v>
-      </c>
       <c r="H583" t="s">
         <v>23</v>
       </c>
@@ -29087,9 +28458,6 @@
       <c r="F584">
         <v>18</v>
       </c>
-      <c r="G584">
-        <v>13</v>
-      </c>
       <c r="H584" t="s">
         <v>16</v>
       </c>
@@ -29263,9 +28631,6 @@
       <c r="F588">
         <v>12</v>
       </c>
-      <c r="G588">
-        <v>13</v>
-      </c>
       <c r="H588" t="s">
         <v>16</v>
       </c>
@@ -29307,9 +28672,6 @@
       <c r="F589">
         <v>13</v>
       </c>
-      <c r="G589">
-        <v>8</v>
-      </c>
       <c r="H589" t="s">
         <v>16</v>
       </c>
@@ -29351,9 +28713,6 @@
       <c r="F590">
         <v>17</v>
       </c>
-      <c r="G590">
-        <v>8</v>
-      </c>
       <c r="H590" t="s">
         <v>23</v>
       </c>
@@ -29395,9 +28754,6 @@
       <c r="F591">
         <v>16</v>
       </c>
-      <c r="G591">
-        <v>9</v>
-      </c>
       <c r="H591" t="s">
         <v>23</v>
       </c>
@@ -29571,9 +28927,6 @@
       <c r="F595">
         <v>24</v>
       </c>
-      <c r="G595">
-        <v>7</v>
-      </c>
       <c r="H595" t="s">
         <v>23</v>
       </c>
@@ -29659,9 +29012,6 @@
       <c r="F597">
         <v>10</v>
       </c>
-      <c r="G597">
-        <v>9</v>
-      </c>
       <c r="H597" t="s">
         <v>23</v>
       </c>
@@ -29748,7 +29098,7 @@
         <v>10</v>
       </c>
       <c r="G599">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H599" t="s">
         <v>16</v>
@@ -29835,9 +29185,6 @@
       <c r="F601">
         <v>17</v>
       </c>
-      <c r="G601">
-        <v>13</v>
-      </c>
       <c r="H601" t="s">
         <v>23</v>
       </c>
@@ -30055,9 +29402,6 @@
       <c r="F606">
         <v>14</v>
       </c>
-      <c r="G606">
-        <v>13</v>
-      </c>
       <c r="H606" t="s">
         <v>16</v>
       </c>
@@ -30187,9 +29531,6 @@
       <c r="F609">
         <v>10</v>
       </c>
-      <c r="G609">
-        <v>9</v>
-      </c>
       <c r="H609" t="s">
         <v>16</v>
       </c>
@@ -30275,9 +29616,6 @@
       <c r="F611">
         <v>16</v>
       </c>
-      <c r="G611">
-        <v>13</v>
-      </c>
       <c r="H611" t="s">
         <v>16</v>
       </c>
@@ -30319,9 +29657,6 @@
       <c r="F612">
         <v>24</v>
       </c>
-      <c r="G612">
-        <v>7</v>
-      </c>
       <c r="H612" t="s">
         <v>16</v>
       </c>
@@ -30407,9 +29742,6 @@
       <c r="F614">
         <v>16</v>
       </c>
-      <c r="G614">
-        <v>8</v>
-      </c>
       <c r="H614" t="s">
         <v>16</v>
       </c>
@@ -30495,9 +29827,6 @@
       <c r="F616">
         <v>10</v>
       </c>
-      <c r="G616">
-        <v>9</v>
-      </c>
       <c r="H616" t="s">
         <v>16</v>
       </c>
@@ -30539,9 +29868,6 @@
       <c r="F617">
         <v>19</v>
       </c>
-      <c r="G617">
-        <v>13</v>
-      </c>
       <c r="H617" t="s">
         <v>16</v>
       </c>
@@ -30672,7 +29998,7 @@
         <v>23</v>
       </c>
       <c r="G620">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H620" t="s">
         <v>16</v>
@@ -30715,9 +30041,6 @@
       <c r="F621">
         <v>22</v>
       </c>
-      <c r="G621">
-        <v>7</v>
-      </c>
       <c r="H621" t="s">
         <v>16</v>
       </c>
@@ -30891,9 +30214,6 @@
       <c r="F625">
         <v>18</v>
       </c>
-      <c r="G625">
-        <v>7</v>
-      </c>
       <c r="H625" t="s">
         <v>23</v>
       </c>
@@ -31067,9 +30387,6 @@
       <c r="F629">
         <v>14</v>
       </c>
-      <c r="G629">
-        <v>9</v>
-      </c>
       <c r="H629" t="s">
         <v>16</v>
       </c>
@@ -31155,9 +30472,6 @@
       <c r="F631">
         <v>21</v>
       </c>
-      <c r="G631">
-        <v>13</v>
-      </c>
       <c r="H631" t="s">
         <v>16</v>
       </c>
@@ -31243,9 +30557,6 @@
       <c r="F633">
         <v>19</v>
       </c>
-      <c r="G633">
-        <v>13</v>
-      </c>
       <c r="H633" t="s">
         <v>16</v>
       </c>
@@ -31287,9 +30598,6 @@
       <c r="F634">
         <v>15</v>
       </c>
-      <c r="G634">
-        <v>13</v>
-      </c>
       <c r="H634" t="s">
         <v>16</v>
       </c>
@@ -31463,9 +30771,6 @@
       <c r="F638">
         <v>23</v>
       </c>
-      <c r="G638">
-        <v>7</v>
-      </c>
       <c r="H638" t="s">
         <v>23</v>
       </c>
@@ -31551,9 +30856,6 @@
       <c r="F640">
         <v>14</v>
       </c>
-      <c r="G640">
-        <v>13</v>
-      </c>
       <c r="H640" t="s">
         <v>16</v>
       </c>
@@ -31683,9 +30985,6 @@
       <c r="F643">
         <v>24</v>
       </c>
-      <c r="G643">
-        <v>13</v>
-      </c>
       <c r="H643" t="s">
         <v>23</v>
       </c>
@@ -31947,9 +31246,6 @@
       <c r="F649">
         <v>21</v>
       </c>
-      <c r="G649">
-        <v>9</v>
-      </c>
       <c r="H649" t="s">
         <v>16</v>
       </c>
@@ -31991,9 +31287,6 @@
       <c r="F650">
         <v>15</v>
       </c>
-      <c r="G650">
-        <v>13</v>
-      </c>
       <c r="H650" t="s">
         <v>16</v>
       </c>
@@ -32035,9 +31328,6 @@
       <c r="F651">
         <v>16</v>
       </c>
-      <c r="G651">
-        <v>13</v>
-      </c>
       <c r="H651" t="s">
         <v>16</v>
       </c>
@@ -32167,9 +31457,6 @@
       <c r="F654">
         <v>19</v>
       </c>
-      <c r="G654">
-        <v>8</v>
-      </c>
       <c r="H654" t="s">
         <v>16</v>
       </c>
@@ -32211,9 +31498,6 @@
       <c r="F655">
         <v>12</v>
       </c>
-      <c r="G655">
-        <v>9</v>
-      </c>
       <c r="H655" t="s">
         <v>23</v>
       </c>
@@ -32299,9 +31583,6 @@
       <c r="F657">
         <v>19</v>
       </c>
-      <c r="G657">
-        <v>8</v>
-      </c>
       <c r="H657" t="s">
         <v>16</v>
       </c>
@@ -32343,9 +31624,6 @@
       <c r="F658">
         <v>11</v>
       </c>
-      <c r="G658">
-        <v>13</v>
-      </c>
       <c r="H658" t="s">
         <v>16</v>
       </c>
@@ -32387,9 +31665,6 @@
       <c r="F659">
         <v>10</v>
       </c>
-      <c r="G659">
-        <v>13</v>
-      </c>
       <c r="H659" t="s">
         <v>16</v>
       </c>
@@ -32475,9 +31750,6 @@
       <c r="F661">
         <v>16</v>
       </c>
-      <c r="G661">
-        <v>7</v>
-      </c>
       <c r="H661" t="s">
         <v>23</v>
       </c>
@@ -32519,9 +31791,6 @@
       <c r="F662">
         <v>21</v>
       </c>
-      <c r="G662">
-        <v>5</v>
-      </c>
       <c r="H662" t="s">
         <v>16</v>
       </c>
@@ -32695,9 +31964,6 @@
       <c r="F666">
         <v>20</v>
       </c>
-      <c r="G666">
-        <v>5</v>
-      </c>
       <c r="H666" t="s">
         <v>23</v>
       </c>
@@ -32739,9 +32005,6 @@
       <c r="F667">
         <v>22</v>
       </c>
-      <c r="G667">
-        <v>7</v>
-      </c>
       <c r="H667" t="s">
         <v>23</v>
       </c>
@@ -32827,9 +32090,6 @@
       <c r="F669">
         <v>21</v>
       </c>
-      <c r="G669">
-        <v>7</v>
-      </c>
       <c r="H669" t="s">
         <v>16</v>
       </c>
@@ -33003,9 +32263,6 @@
       <c r="F673">
         <v>16</v>
       </c>
-      <c r="G673">
-        <v>13</v>
-      </c>
       <c r="H673" t="s">
         <v>23</v>
       </c>
@@ -33047,9 +32304,6 @@
       <c r="F674">
         <v>14</v>
       </c>
-      <c r="G674">
-        <v>9</v>
-      </c>
       <c r="H674" t="s">
         <v>16</v>
       </c>
@@ -33135,9 +32389,6 @@
       <c r="F676">
         <v>21</v>
       </c>
-      <c r="G676">
-        <v>8</v>
-      </c>
       <c r="H676" t="s">
         <v>23</v>
       </c>
@@ -33267,9 +32518,6 @@
       <c r="F679">
         <v>10</v>
       </c>
-      <c r="G679">
-        <v>8</v>
-      </c>
       <c r="H679" t="s">
         <v>23</v>
       </c>
@@ -33311,9 +32559,6 @@
       <c r="F680">
         <v>10</v>
       </c>
-      <c r="G680">
-        <v>13</v>
-      </c>
       <c r="H680" t="s">
         <v>23</v>
       </c>
@@ -33443,9 +32688,6 @@
       <c r="F683">
         <v>12</v>
       </c>
-      <c r="G683">
-        <v>13</v>
-      </c>
       <c r="H683" t="s">
         <v>16</v>
       </c>
@@ -33487,9 +32729,6 @@
       <c r="F684">
         <v>10</v>
       </c>
-      <c r="G684">
-        <v>13</v>
-      </c>
       <c r="H684" t="s">
         <v>16</v>
       </c>
@@ -33531,9 +32770,6 @@
       <c r="F685">
         <v>12</v>
       </c>
-      <c r="G685">
-        <v>9</v>
-      </c>
       <c r="H685" t="s">
         <v>23</v>
       </c>
@@ -33795,9 +33031,6 @@
       <c r="F691">
         <v>26</v>
       </c>
-      <c r="G691">
-        <v>8</v>
-      </c>
       <c r="H691" t="s">
         <v>16</v>
       </c>
@@ -33971,9 +33204,6 @@
       <c r="F695">
         <v>14</v>
       </c>
-      <c r="G695">
-        <v>13</v>
-      </c>
       <c r="H695" t="s">
         <v>16</v>
       </c>
@@ -34015,9 +33245,6 @@
       <c r="F696">
         <v>18</v>
       </c>
-      <c r="G696">
-        <v>13</v>
-      </c>
       <c r="H696" t="s">
         <v>16</v>
       </c>
@@ -34059,9 +33286,6 @@
       <c r="F697">
         <v>18</v>
       </c>
-      <c r="G697">
-        <v>13</v>
-      </c>
       <c r="H697" t="s">
         <v>23</v>
       </c>
@@ -34191,9 +33415,6 @@
       <c r="F700">
         <v>18</v>
       </c>
-      <c r="G700">
-        <v>13</v>
-      </c>
       <c r="H700" t="s">
         <v>16</v>
       </c>
@@ -34235,9 +33456,6 @@
       <c r="F701">
         <v>19</v>
       </c>
-      <c r="G701">
-        <v>8</v>
-      </c>
       <c r="H701" t="s">
         <v>16</v>
       </c>
@@ -34411,9 +33629,6 @@
       <c r="F705">
         <v>26</v>
       </c>
-      <c r="G705">
-        <v>13</v>
-      </c>
       <c r="H705" t="s">
         <v>16</v>
       </c>
@@ -34499,9 +33714,6 @@
       <c r="F707">
         <v>16</v>
       </c>
-      <c r="G707">
-        <v>13</v>
-      </c>
       <c r="H707" t="s">
         <v>16</v>
       </c>
@@ -34543,9 +33755,6 @@
       <c r="F708">
         <v>17</v>
       </c>
-      <c r="G708">
-        <v>7</v>
-      </c>
       <c r="H708" t="s">
         <v>23</v>
       </c>
@@ -34587,9 +33796,6 @@
       <c r="F709">
         <v>10</v>
       </c>
-      <c r="G709">
-        <v>9</v>
-      </c>
       <c r="H709" t="s">
         <v>23</v>
       </c>
@@ -34631,9 +33837,6 @@
       <c r="F710">
         <v>15</v>
       </c>
-      <c r="G710">
-        <v>8</v>
-      </c>
       <c r="H710" t="s">
         <v>16</v>
       </c>
@@ -34675,9 +33878,6 @@
       <c r="F711">
         <v>18</v>
       </c>
-      <c r="G711">
-        <v>9</v>
-      </c>
       <c r="H711" t="s">
         <v>16</v>
       </c>
@@ -34807,9 +34007,6 @@
       <c r="F714">
         <v>18</v>
       </c>
-      <c r="G714">
-        <v>7</v>
-      </c>
       <c r="H714" t="s">
         <v>16</v>
       </c>
@@ -34983,9 +34180,6 @@
       <c r="F718">
         <v>19</v>
       </c>
-      <c r="G718">
-        <v>5</v>
-      </c>
       <c r="H718" t="s">
         <v>23</v>
       </c>
@@ -35071,9 +34265,6 @@
       <c r="F720">
         <v>18</v>
       </c>
-      <c r="G720">
-        <v>13</v>
-      </c>
       <c r="H720" t="s">
         <v>16</v>
       </c>
@@ -35379,9 +34570,6 @@
       <c r="F727">
         <v>10</v>
       </c>
-      <c r="G727">
-        <v>13</v>
-      </c>
       <c r="H727" t="s">
         <v>16</v>
       </c>
@@ -35423,9 +34611,6 @@
       <c r="F728">
         <v>24</v>
       </c>
-      <c r="G728">
-        <v>9</v>
-      </c>
       <c r="H728" t="s">
         <v>23</v>
       </c>
@@ -35467,9 +34652,6 @@
       <c r="F729">
         <v>17</v>
       </c>
-      <c r="G729">
-        <v>7</v>
-      </c>
       <c r="H729" t="s">
         <v>23</v>
       </c>
@@ -35555,9 +34737,6 @@
       <c r="F731">
         <v>16</v>
       </c>
-      <c r="G731">
-        <v>8</v>
-      </c>
       <c r="H731" t="s">
         <v>16</v>
       </c>
@@ -35599,9 +34778,6 @@
       <c r="F732">
         <v>19</v>
       </c>
-      <c r="G732">
-        <v>8</v>
-      </c>
       <c r="H732" t="s">
         <v>16</v>
       </c>
@@ -35731,9 +34907,6 @@
       <c r="F735">
         <v>16</v>
       </c>
-      <c r="G735">
-        <v>8</v>
-      </c>
       <c r="H735" t="s">
         <v>16</v>
       </c>
@@ -35907,9 +35080,6 @@
       <c r="F739">
         <v>18</v>
       </c>
-      <c r="G739">
-        <v>8</v>
-      </c>
       <c r="H739" t="s">
         <v>16</v>
       </c>
@@ -36039,9 +35209,6 @@
       <c r="F742">
         <v>23</v>
       </c>
-      <c r="G742">
-        <v>8</v>
-      </c>
       <c r="H742" t="s">
         <v>16</v>
       </c>
@@ -36127,9 +35294,6 @@
       <c r="F744">
         <v>20</v>
       </c>
-      <c r="G744">
-        <v>7</v>
-      </c>
       <c r="H744" t="s">
         <v>16</v>
       </c>
@@ -36391,9 +35555,6 @@
       <c r="F750">
         <v>14</v>
       </c>
-      <c r="G750">
-        <v>13</v>
-      </c>
       <c r="H750" t="s">
         <v>16</v>
       </c>
@@ -36523,9 +35684,6 @@
       <c r="F753">
         <v>16</v>
       </c>
-      <c r="G753">
-        <v>9</v>
-      </c>
       <c r="H753" t="s">
         <v>16</v>
       </c>
@@ -36655,9 +35813,6 @@
       <c r="F756">
         <v>20</v>
       </c>
-      <c r="G756">
-        <v>13</v>
-      </c>
       <c r="H756" t="s">
         <v>16</v>
       </c>
@@ -36919,9 +36074,6 @@
       <c r="F762">
         <v>25</v>
       </c>
-      <c r="G762">
-        <v>8</v>
-      </c>
       <c r="H762" t="s">
         <v>16</v>
       </c>
@@ -37051,9 +36203,6 @@
       <c r="F765">
         <v>26</v>
       </c>
-      <c r="G765">
-        <v>7</v>
-      </c>
       <c r="H765" t="s">
         <v>23</v>
       </c>
@@ -37139,9 +36288,6 @@
       <c r="F767">
         <v>21</v>
       </c>
-      <c r="G767">
-        <v>13</v>
-      </c>
       <c r="H767" t="s">
         <v>23</v>
       </c>
@@ -37271,9 +36417,6 @@
       <c r="F770">
         <v>10</v>
       </c>
-      <c r="G770">
-        <v>13</v>
-      </c>
       <c r="H770" t="s">
         <v>23</v>
       </c>
@@ -37535,9 +36678,6 @@
       <c r="F776">
         <v>13</v>
       </c>
-      <c r="G776">
-        <v>8</v>
-      </c>
       <c r="H776" t="s">
         <v>16</v>
       </c>
@@ -37667,9 +36807,6 @@
       <c r="F779">
         <v>17</v>
       </c>
-      <c r="G779">
-        <v>9</v>
-      </c>
       <c r="H779" t="s">
         <v>16</v>
       </c>
@@ -37843,9 +36980,6 @@
       <c r="F783">
         <v>15</v>
       </c>
-      <c r="G783">
-        <v>13</v>
-      </c>
       <c r="H783" t="s">
         <v>16</v>
       </c>
@@ -37975,9 +37109,6 @@
       <c r="F786">
         <v>11</v>
       </c>
-      <c r="G786">
-        <v>13</v>
-      </c>
       <c r="H786" t="s">
         <v>16</v>
       </c>
@@ -38063,9 +37194,6 @@
       <c r="F788">
         <v>11</v>
       </c>
-      <c r="G788">
-        <v>8</v>
-      </c>
       <c r="H788" t="s">
         <v>16</v>
       </c>
@@ -38107,9 +37235,6 @@
       <c r="F789">
         <v>14</v>
       </c>
-      <c r="G789">
-        <v>13</v>
-      </c>
       <c r="H789" t="s">
         <v>16</v>
       </c>
@@ -38195,9 +37320,6 @@
       <c r="F791">
         <v>17</v>
       </c>
-      <c r="G791">
-        <v>13</v>
-      </c>
       <c r="H791" t="s">
         <v>16</v>
       </c>
@@ -38327,9 +37449,6 @@
       <c r="F794">
         <v>15</v>
       </c>
-      <c r="G794">
-        <v>13</v>
-      </c>
       <c r="H794" t="s">
         <v>23</v>
       </c>
@@ -38415,9 +37534,6 @@
       <c r="F796">
         <v>19</v>
       </c>
-      <c r="G796">
-        <v>8</v>
-      </c>
       <c r="H796" t="s">
         <v>23</v>
       </c>
@@ -38459,9 +37575,6 @@
       <c r="F797">
         <v>14</v>
       </c>
-      <c r="G797">
-        <v>13</v>
-      </c>
       <c r="H797" t="s">
         <v>16</v>
       </c>
@@ -38635,9 +37748,6 @@
       <c r="F801">
         <v>20</v>
       </c>
-      <c r="G801">
-        <v>8</v>
-      </c>
       <c r="H801" t="s">
         <v>16</v>
       </c>
@@ -38723,9 +37833,6 @@
       <c r="F803">
         <v>20</v>
       </c>
-      <c r="G803">
-        <v>13</v>
-      </c>
       <c r="H803" t="s">
         <v>23</v>
       </c>
@@ -38943,9 +38050,6 @@
       <c r="F808">
         <v>24</v>
       </c>
-      <c r="G808">
-        <v>13</v>
-      </c>
       <c r="H808" t="s">
         <v>16</v>
       </c>
@@ -38987,9 +38091,6 @@
       <c r="F809">
         <v>21</v>
       </c>
-      <c r="G809">
-        <v>7</v>
-      </c>
       <c r="H809" t="s">
         <v>16</v>
       </c>
@@ -39031,9 +38132,6 @@
       <c r="F810">
         <v>15</v>
       </c>
-      <c r="G810">
-        <v>8</v>
-      </c>
       <c r="H810" t="s">
         <v>16</v>
       </c>
@@ -39075,9 +38173,6 @@
       <c r="F811">
         <v>12</v>
       </c>
-      <c r="G811">
-        <v>8</v>
-      </c>
       <c r="H811" t="s">
         <v>16</v>
       </c>
@@ -39163,9 +38258,6 @@
       <c r="F813">
         <v>23</v>
       </c>
-      <c r="G813">
-        <v>5</v>
-      </c>
       <c r="H813" t="s">
         <v>16</v>
       </c>
@@ -39207,9 +38299,6 @@
       <c r="F814">
         <v>18</v>
       </c>
-      <c r="G814">
-        <v>9</v>
-      </c>
       <c r="H814" t="s">
         <v>16</v>
       </c>
@@ -39339,9 +38428,6 @@
       <c r="F817">
         <v>17</v>
       </c>
-      <c r="G817">
-        <v>8</v>
-      </c>
       <c r="H817" t="s">
         <v>16</v>
       </c>
@@ -39515,9 +38601,6 @@
       <c r="F821">
         <v>13</v>
       </c>
-      <c r="G821">
-        <v>13</v>
-      </c>
       <c r="H821" t="s">
         <v>16</v>
       </c>
@@ -39603,9 +38686,6 @@
       <c r="F823">
         <v>10</v>
       </c>
-      <c r="G823">
-        <v>13</v>
-      </c>
       <c r="H823" t="s">
         <v>16</v>
       </c>
@@ -39647,9 +38727,6 @@
       <c r="F824">
         <v>12</v>
       </c>
-      <c r="G824">
-        <v>13</v>
-      </c>
       <c r="H824" t="s">
         <v>23</v>
       </c>
@@ -39735,9 +38812,6 @@
       <c r="F826">
         <v>14</v>
       </c>
-      <c r="G826">
-        <v>13</v>
-      </c>
       <c r="H826" t="s">
         <v>23</v>
       </c>
@@ -39779,9 +38853,6 @@
       <c r="F827">
         <v>25</v>
       </c>
-      <c r="G827">
-        <v>8</v>
-      </c>
       <c r="H827" t="s">
         <v>23</v>
       </c>
@@ -39911,9 +38982,6 @@
       <c r="F830">
         <v>12</v>
       </c>
-      <c r="G830">
-        <v>8</v>
-      </c>
       <c r="H830" t="s">
         <v>16</v>
       </c>
@@ -40219,9 +39287,6 @@
       <c r="F837">
         <v>15</v>
       </c>
-      <c r="G837">
-        <v>11</v>
-      </c>
       <c r="H837" t="s">
         <v>16</v>
       </c>
@@ -40263,9 +39328,6 @@
       <c r="F838">
         <v>11</v>
       </c>
-      <c r="G838">
-        <v>7</v>
-      </c>
       <c r="H838" t="s">
         <v>16</v>
       </c>
@@ -40615,9 +39677,6 @@
       <c r="F846">
         <v>13</v>
       </c>
-      <c r="G846">
-        <v>13</v>
-      </c>
       <c r="H846" t="s">
         <v>16</v>
       </c>
@@ -40703,9 +39762,6 @@
       <c r="F848">
         <v>21</v>
       </c>
-      <c r="G848">
-        <v>9</v>
-      </c>
       <c r="H848" t="s">
         <v>23</v>
       </c>
@@ -40791,9 +39847,6 @@
       <c r="F850">
         <v>17</v>
       </c>
-      <c r="G850">
-        <v>13</v>
-      </c>
       <c r="H850" t="s">
         <v>23</v>
       </c>
@@ -40835,9 +39888,6 @@
       <c r="F851">
         <v>21</v>
       </c>
-      <c r="G851">
-        <v>9</v>
-      </c>
       <c r="H851" t="s">
         <v>16</v>
       </c>
@@ -41055,9 +40105,6 @@
       <c r="F856">
         <v>15</v>
       </c>
-      <c r="G856">
-        <v>9</v>
-      </c>
       <c r="H856" t="s">
         <v>23</v>
       </c>
@@ -41143,9 +40190,6 @@
       <c r="F858">
         <v>19</v>
       </c>
-      <c r="G858">
-        <v>9</v>
-      </c>
       <c r="H858" t="s">
         <v>16</v>
       </c>
@@ -41187,9 +40231,6 @@
       <c r="F859">
         <v>15</v>
       </c>
-      <c r="G859">
-        <v>7</v>
-      </c>
       <c r="H859" t="s">
         <v>16</v>
       </c>
@@ -41363,9 +40404,6 @@
       <c r="F863">
         <v>15</v>
       </c>
-      <c r="G863">
-        <v>13</v>
-      </c>
       <c r="H863" t="s">
         <v>16</v>
       </c>
@@ -41495,9 +40533,6 @@
       <c r="F866">
         <v>21</v>
       </c>
-      <c r="G866">
-        <v>9</v>
-      </c>
       <c r="H866" t="s">
         <v>23</v>
       </c>
@@ -41583,9 +40618,6 @@
       <c r="F868">
         <v>23</v>
       </c>
-      <c r="G868">
-        <v>9</v>
-      </c>
       <c r="H868" t="s">
         <v>16</v>
       </c>
@@ -41627,9 +40659,6 @@
       <c r="F869">
         <v>20</v>
       </c>
-      <c r="G869">
-        <v>9</v>
-      </c>
       <c r="H869" t="s">
         <v>16</v>
       </c>
@@ -41803,9 +40832,6 @@
       <c r="F873">
         <v>18</v>
       </c>
-      <c r="G873">
-        <v>5</v>
-      </c>
       <c r="H873" t="s">
         <v>16</v>
       </c>
@@ -41847,9 +40873,6 @@
       <c r="F874">
         <v>15</v>
       </c>
-      <c r="G874">
-        <v>13</v>
-      </c>
       <c r="H874" t="s">
         <v>16</v>
       </c>
@@ -41935,9 +40958,6 @@
       <c r="F876">
         <v>19</v>
       </c>
-      <c r="G876">
-        <v>13</v>
-      </c>
       <c r="H876" t="s">
         <v>16</v>
       </c>
@@ -41979,9 +40999,6 @@
       <c r="F877">
         <v>15</v>
       </c>
-      <c r="G877">
-        <v>13</v>
-      </c>
       <c r="H877" t="s">
         <v>16</v>
       </c>
@@ -42023,9 +41040,6 @@
       <c r="F878">
         <v>18</v>
       </c>
-      <c r="G878">
-        <v>13</v>
-      </c>
       <c r="H878" t="s">
         <v>23</v>
       </c>
@@ -42155,9 +41169,6 @@
       <c r="F881">
         <v>16</v>
       </c>
-      <c r="G881">
-        <v>13</v>
-      </c>
       <c r="H881" t="s">
         <v>23</v>
       </c>
@@ -42287,9 +41298,6 @@
       <c r="F884">
         <v>16</v>
       </c>
-      <c r="G884">
-        <v>13</v>
-      </c>
       <c r="H884" t="s">
         <v>16</v>
       </c>
@@ -42331,9 +41339,6 @@
       <c r="F885">
         <v>17</v>
       </c>
-      <c r="G885">
-        <v>9</v>
-      </c>
       <c r="H885" t="s">
         <v>16</v>
       </c>
@@ -42375,9 +41380,6 @@
       <c r="F886">
         <v>16</v>
       </c>
-      <c r="G886">
-        <v>13</v>
-      </c>
       <c r="H886" t="s">
         <v>16</v>
       </c>
@@ -42727,9 +41729,6 @@
       <c r="F894">
         <v>25</v>
       </c>
-      <c r="G894">
-        <v>13</v>
-      </c>
       <c r="H894" t="s">
         <v>16</v>
       </c>
@@ -42771,9 +41770,6 @@
       <c r="F895">
         <v>17</v>
       </c>
-      <c r="G895">
-        <v>9</v>
-      </c>
       <c r="H895" t="s">
         <v>16</v>
       </c>
@@ -42947,9 +41943,6 @@
       <c r="F899">
         <v>11</v>
       </c>
-      <c r="G899">
-        <v>13</v>
-      </c>
       <c r="H899" t="s">
         <v>23</v>
       </c>
@@ -42991,9 +41984,6 @@
       <c r="F900">
         <v>21</v>
       </c>
-      <c r="G900">
-        <v>13</v>
-      </c>
       <c r="H900" t="s">
         <v>16</v>
       </c>
@@ -43167,9 +42157,6 @@
       <c r="F904">
         <v>18</v>
       </c>
-      <c r="G904">
-        <v>9</v>
-      </c>
       <c r="H904" t="s">
         <v>16</v>
       </c>
@@ -43211,9 +42198,6 @@
       <c r="F905">
         <v>15</v>
       </c>
-      <c r="G905">
-        <v>5</v>
-      </c>
       <c r="H905" t="s">
         <v>16</v>
       </c>
@@ -43255,9 +42239,6 @@
       <c r="F906">
         <v>19</v>
       </c>
-      <c r="G906">
-        <v>7</v>
-      </c>
       <c r="H906" t="s">
         <v>16</v>
       </c>
@@ -43695,9 +42676,6 @@
       <c r="F916">
         <v>11</v>
       </c>
-      <c r="G916">
-        <v>9</v>
-      </c>
       <c r="H916" t="s">
         <v>23</v>
       </c>
@@ -43783,9 +42761,6 @@
       <c r="F918">
         <v>20</v>
       </c>
-      <c r="G918">
-        <v>8</v>
-      </c>
       <c r="H918" t="s">
         <v>16</v>
       </c>
@@ -43827,9 +42802,6 @@
       <c r="F919">
         <v>10</v>
       </c>
-      <c r="G919">
-        <v>13</v>
-      </c>
       <c r="H919" t="s">
         <v>16</v>
       </c>
@@ -44003,9 +42975,6 @@
       <c r="F923">
         <v>24</v>
       </c>
-      <c r="G923">
-        <v>5</v>
-      </c>
       <c r="H923" t="s">
         <v>16</v>
       </c>
@@ -44091,9 +43060,6 @@
       <c r="F925">
         <v>12</v>
       </c>
-      <c r="G925">
-        <v>13</v>
-      </c>
       <c r="H925" t="s">
         <v>16</v>
       </c>
@@ -44135,9 +43101,6 @@
       <c r="F926">
         <v>18</v>
       </c>
-      <c r="G926">
-        <v>13</v>
-      </c>
       <c r="H926" t="s">
         <v>23</v>
       </c>
@@ -44267,9 +43230,6 @@
       <c r="F929">
         <v>17</v>
       </c>
-      <c r="G929">
-        <v>7</v>
-      </c>
       <c r="H929" t="s">
         <v>23</v>
       </c>
@@ -44355,9 +43315,6 @@
       <c r="F931">
         <v>16</v>
       </c>
-      <c r="G931">
-        <v>13</v>
-      </c>
       <c r="H931" t="s">
         <v>16</v>
       </c>
@@ -44443,9 +43400,6 @@
       <c r="F933">
         <v>16</v>
       </c>
-      <c r="G933">
-        <v>8</v>
-      </c>
       <c r="H933" t="s">
         <v>23</v>
       </c>
@@ -44487,9 +43441,6 @@
       <c r="F934">
         <v>19</v>
       </c>
-      <c r="G934">
-        <v>11</v>
-      </c>
       <c r="H934" t="s">
         <v>16</v>
       </c>
@@ -44663,9 +43614,6 @@
       <c r="F938">
         <v>16</v>
       </c>
-      <c r="G938">
-        <v>8</v>
-      </c>
       <c r="H938" t="s">
         <v>23</v>
       </c>
@@ -44883,9 +43831,6 @@
       <c r="F943">
         <v>18</v>
       </c>
-      <c r="G943">
-        <v>13</v>
-      </c>
       <c r="H943" t="s">
         <v>16</v>
       </c>
@@ -44927,9 +43872,6 @@
       <c r="F944">
         <v>15</v>
       </c>
-      <c r="G944">
-        <v>7</v>
-      </c>
       <c r="H944" t="s">
         <v>23</v>
       </c>
@@ -45015,9 +43957,6 @@
       <c r="F946">
         <v>19</v>
       </c>
-      <c r="G946">
-        <v>13</v>
-      </c>
       <c r="H946" t="s">
         <v>16</v>
       </c>
@@ -45191,9 +44130,6 @@
       <c r="F950">
         <v>24</v>
       </c>
-      <c r="G950">
-        <v>13</v>
-      </c>
       <c r="H950" t="s">
         <v>16</v>
       </c>
@@ -45323,9 +44259,6 @@
       <c r="F953">
         <v>16</v>
       </c>
-      <c r="G953">
-        <v>13</v>
-      </c>
       <c r="H953" t="s">
         <v>16</v>
       </c>
@@ -45543,9 +44476,6 @@
       <c r="F958">
         <v>26</v>
       </c>
-      <c r="G958">
-        <v>13</v>
-      </c>
       <c r="H958" t="s">
         <v>16</v>
       </c>
@@ -45719,9 +44649,6 @@
       <c r="F962">
         <v>16</v>
       </c>
-      <c r="G962">
-        <v>13</v>
-      </c>
       <c r="H962" t="s">
         <v>16</v>
       </c>
@@ -45807,9 +44734,6 @@
       <c r="F964">
         <v>14</v>
       </c>
-      <c r="G964">
-        <v>13</v>
-      </c>
       <c r="H964" t="s">
         <v>16</v>
       </c>
@@ -46027,9 +44951,6 @@
       <c r="F969">
         <v>17</v>
       </c>
-      <c r="G969">
-        <v>9</v>
-      </c>
       <c r="H969" t="s">
         <v>16</v>
       </c>
@@ -46203,9 +45124,6 @@
       <c r="F973">
         <v>23</v>
       </c>
-      <c r="G973">
-        <v>9</v>
-      </c>
       <c r="H973" t="s">
         <v>23</v>
       </c>
@@ -46379,9 +45297,6 @@
       <c r="F977">
         <v>14</v>
       </c>
-      <c r="G977">
-        <v>13</v>
-      </c>
       <c r="H977" t="s">
         <v>16</v>
       </c>
@@ -46511,9 +45426,6 @@
       <c r="F980">
         <v>22</v>
       </c>
-      <c r="G980">
-        <v>8</v>
-      </c>
       <c r="H980" t="s">
         <v>16</v>
       </c>
@@ -46555,9 +45467,6 @@
       <c r="F981">
         <v>10</v>
       </c>
-      <c r="G981">
-        <v>13</v>
-      </c>
       <c r="H981" t="s">
         <v>16</v>
       </c>
@@ -46819,9 +45728,6 @@
       <c r="F987">
         <v>21</v>
       </c>
-      <c r="G987">
-        <v>7</v>
-      </c>
       <c r="H987" t="s">
         <v>16</v>
       </c>
@@ -46863,9 +45769,6 @@
       <c r="F988">
         <v>15</v>
       </c>
-      <c r="G988">
-        <v>13</v>
-      </c>
       <c r="H988" t="s">
         <v>16</v>
       </c>
@@ -46907,9 +45810,6 @@
       <c r="F989">
         <v>18</v>
       </c>
-      <c r="G989">
-        <v>13</v>
-      </c>
       <c r="H989" t="s">
         <v>16</v>
       </c>
@@ -46951,9 +45851,6 @@
       <c r="F990">
         <v>16</v>
       </c>
-      <c r="G990">
-        <v>7</v>
-      </c>
       <c r="H990" t="s">
         <v>16</v>
       </c>
@@ -46995,9 +45892,6 @@
       <c r="F991">
         <v>19</v>
       </c>
-      <c r="G991">
-        <v>13</v>
-      </c>
       <c r="H991" t="s">
         <v>16</v>
       </c>
@@ -47127,9 +46021,6 @@
       <c r="F994">
         <v>12</v>
       </c>
-      <c r="G994">
-        <v>7</v>
-      </c>
       <c r="H994" t="s">
         <v>23</v>
       </c>
@@ -47215,9 +46106,6 @@
       <c r="F996">
         <v>17</v>
       </c>
-      <c r="G996">
-        <v>8</v>
-      </c>
       <c r="H996" t="s">
         <v>23</v>
       </c>
@@ -47303,9 +46191,6 @@
       <c r="F998">
         <v>19</v>
       </c>
-      <c r="G998">
-        <v>9</v>
-      </c>
       <c r="H998" t="s">
         <v>16</v>
       </c>
@@ -47434,9 +46319,6 @@
       </c>
       <c r="F1001">
         <v>24</v>
-      </c>
-      <c r="G1001">
-        <v>13</v>
       </c>
       <c r="H1001" t="s">
         <v>16</v>
